--- a/seed/files/SOW_subs_pricing_contractor_info.xlsx
+++ b/seed/files/SOW_subs_pricing_contractor_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\COMPANY INFORMATION\MCH\WORKFLOW PROCESSES\MARIA LEAVING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F668F12-6009-43D8-9CBD-342165DFB63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{065148F2-87B0-4074-B843-A067A6A4EA05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4BA3835-FF45-4079-8868-42924AA49BFD}"/>
+    <workbookView xWindow="-25500" yWindow="600" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{F4BA3835-FF45-4079-8868-42924AA49BFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Purchasing" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="387">
   <si>
     <t>DESCRIPTION</t>
   </si>
@@ -830,9 +830,6 @@
     <t>832-840-6048</t>
   </si>
   <si>
-    <t>reqeust all pricing, schedule all work, inspections, punchout, issues, etc.</t>
-  </si>
-  <si>
     <t>1stdefensefi@gmail.com</t>
   </si>
   <si>
@@ -1167,13 +1164,49 @@
   </si>
   <si>
     <t>832-376-8969</t>
+  </si>
+  <si>
+    <t>THIRD PARTY ENERGY INSPECTION</t>
+  </si>
+  <si>
+    <t>Twin Lakes Energy Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mike  </t>
+  </si>
+  <si>
+    <t>301-247-8478</t>
+  </si>
+  <si>
+    <t>request all pricing, schedule all work, inspections, punchout, issues, etc.</t>
+  </si>
+  <si>
+    <t>tlenergyconsulting@gmail.com</t>
+  </si>
+  <si>
+    <t>request all plan review and city of houston documents for permitting, schedule all inspections for insulation and for final energy inspections</t>
+  </si>
+  <si>
+    <t>THIRD PARTY STUCCO INSPECTION</t>
+  </si>
+  <si>
+    <t>Exterior inspections</t>
+  </si>
+  <si>
+    <t>April Rigney</t>
+  </si>
+  <si>
+    <t>scheduling@exteriorinspections.com</t>
+  </si>
+  <si>
+    <t>schedule all lathe inspections</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1200,6 +1233,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1235,7 +1274,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1250,6 +1289,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2344,7 +2384,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45EAC501-7979-4DE2-810D-2E0831EA7B78}">
-  <dimension ref="A3:E102"/>
+  <dimension ref="A3:E105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" customWidth="1"/>
@@ -2848,613 +2888,652 @@
         <v>262</v>
       </c>
       <c r="E45" t="s">
-        <v>263</v>
+        <v>379</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D46" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>71</v>
+        <v>375</v>
       </c>
       <c r="B47" t="s">
-        <v>265</v>
+        <v>376</v>
       </c>
       <c r="C47" t="s">
-        <v>266</v>
-      </c>
-      <c r="D47" t="s">
-        <v>267</v>
+        <v>377</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>378</v>
       </c>
       <c r="E47" t="s">
-        <v>268</v>
+        <v>381</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D48" s="4" t="s">
-        <v>269</v>
+        <v>380</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B49" t="s">
-        <v>270</v>
+        <v>264</v>
+      </c>
+      <c r="C49" t="s">
+        <v>265</v>
+      </c>
+      <c r="D49" t="s">
+        <v>266</v>
+      </c>
+      <c r="E49" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>79</v>
-      </c>
-      <c r="B50" t="s">
-        <v>271</v>
-      </c>
-      <c r="C50" t="s">
-        <v>272</v>
-      </c>
-      <c r="D50" t="s">
-        <v>273</v>
-      </c>
-      <c r="E50" t="s">
-        <v>274</v>
+      <c r="D50" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>382</v>
+      </c>
+      <c r="B51" t="s">
+        <v>383</v>
+      </c>
+      <c r="C51" t="s">
+        <v>384</v>
+      </c>
       <c r="D51" s="4" t="s">
-        <v>275</v>
+        <v>385</v>
+      </c>
+      <c r="E51" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>76</v>
+      </c>
+      <c r="B52" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>79</v>
+      </c>
+      <c r="B53" t="s">
+        <v>270</v>
+      </c>
+      <c r="C53" t="s">
+        <v>271</v>
+      </c>
+      <c r="D53" t="s">
+        <v>272</v>
+      </c>
+      <c r="E53" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D54" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>82</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B55" t="s">
+        <v>275</v>
+      </c>
+      <c r="C55" t="s">
         <v>276</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D55" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="E55" t="s">
         <v>278</v>
       </c>
-      <c r="E52" t="s">
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D53" t="s">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>88</v>
+      </c>
+      <c r="B57" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>88</v>
-      </c>
-      <c r="B54" t="s">
+      <c r="C57" t="s">
         <v>281</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D57" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="E57" t="s">
         <v>283</v>
       </c>
-      <c r="E54" t="s">
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C58" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C55" t="s">
+      <c r="D58" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="E58" t="s">
         <v>286</v>
       </c>
-      <c r="E55" t="s">
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="B59" t="s">
+        <v>198</v>
+      </c>
+      <c r="C59" t="s">
+        <v>199</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E59" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>93</v>
+      </c>
+      <c r="B61" t="s">
         <v>288</v>
       </c>
-      <c r="B56" t="s">
-        <v>198</v>
-      </c>
-      <c r="C56" t="s">
-        <v>199</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="E56" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D57" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>93</v>
-      </c>
-      <c r="B58" t="s">
+      <c r="C61" t="s">
         <v>289</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D61" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="E61" t="s">
         <v>291</v>
       </c>
-      <c r="E58" t="s">
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D59" t="s">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="B63" t="s">
         <v>294</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C63" t="s">
         <v>295</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D63" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="E63" t="s">
         <v>297</v>
       </c>
-      <c r="E60" t="s">
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D61" t="s">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="B65" t="s">
         <v>300</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C65" t="s">
         <v>301</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D65" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="E65" t="s">
         <v>303</v>
       </c>
-      <c r="E62" t="s">
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
         <v>304</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D63" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C64" t="s">
-        <v>306</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="E64" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D65" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C66" t="s">
-        <v>310</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="E66" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
-        <v>313</v>
-      </c>
-      <c r="D67" t="s">
-        <v>314</v>
+        <v>305</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>306</v>
       </c>
       <c r="E67" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>106</v>
-      </c>
-      <c r="B68" t="s">
-        <v>301</v>
-      </c>
-      <c r="C68" t="s">
-        <v>302</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="E68" t="s">
-        <v>304</v>
+      <c r="D68" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D69" t="s">
-        <v>305</v>
+      <c r="C69" t="s">
+        <v>309</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="E69" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
-        <v>306</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>307</v>
+        <v>312</v>
+      </c>
+      <c r="D70" t="s">
+        <v>313</v>
       </c>
       <c r="E70" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D71" t="s">
-        <v>309</v>
+      <c r="A71" t="s">
+        <v>106</v>
+      </c>
+      <c r="B71" t="s">
+        <v>300</v>
+      </c>
+      <c r="C71" t="s">
+        <v>301</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E71" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C72" t="s">
-        <v>310</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="E72" t="s">
-        <v>312</v>
+      <c r="D72" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C73" t="s">
+        <v>305</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="E73" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C75" t="s">
+        <v>309</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="E75" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C76" t="s">
+        <v>312</v>
+      </c>
+      <c r="D76" t="s">
         <v>313</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E76" t="s">
         <v>314</v>
       </c>
-      <c r="E73" t="s">
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>99</v>
+      </c>
+      <c r="B77" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>99</v>
-      </c>
-      <c r="B74" t="s">
+      <c r="C77" t="s">
         <v>316</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D77" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="E77" t="s">
         <v>318</v>
       </c>
-      <c r="E74" t="s">
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
         <v>319</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D75" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>321</v>
-      </c>
-      <c r="B76" t="s">
-        <v>322</v>
-      </c>
-      <c r="C76" t="s">
-        <v>323</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="E76" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D77" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>117</v>
-      </c>
-      <c r="B78" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>121</v>
+        <v>320</v>
       </c>
       <c r="B79" t="s">
-        <v>219</v>
+        <v>321</v>
       </c>
       <c r="C79" t="s">
-        <v>220</v>
+        <v>322</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>221</v>
+        <v>323</v>
       </c>
       <c r="E79" t="s">
-        <v>222</v>
+        <v>324</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D80" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>117</v>
+      </c>
+      <c r="B81" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>121</v>
+      </c>
+      <c r="B82" t="s">
+        <v>219</v>
+      </c>
+      <c r="C82" t="s">
+        <v>220</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E82" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D83" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C81" t="s">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C84" t="s">
         <v>224</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D84" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E84" t="s">
         <v>216</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D82" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>124</v>
-      </c>
-      <c r="B83" t="s">
-        <v>328</v>
-      </c>
-      <c r="C83" t="s">
-        <v>329</v>
-      </c>
-      <c r="D83" t="s">
-        <v>330</v>
-      </c>
-      <c r="E83" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>332</v>
-      </c>
-      <c r="B84" t="s">
-        <v>333</v>
-      </c>
-      <c r="C84" t="s">
-        <v>334</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="E84" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D85" t="s">
-        <v>337</v>
+        <v>226</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>124</v>
+      </c>
+      <c r="B86" t="s">
+        <v>327</v>
+      </c>
+      <c r="C86" t="s">
+        <v>328</v>
+      </c>
+      <c r="D86" t="s">
+        <v>329</v>
+      </c>
+      <c r="E86" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>331</v>
+      </c>
+      <c r="B87" t="s">
+        <v>332</v>
+      </c>
+      <c r="C87" t="s">
+        <v>333</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="E87" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>130</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B89" t="s">
+        <v>337</v>
+      </c>
+      <c r="C89" t="s">
         <v>338</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D89" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="E89" t="s">
         <v>340</v>
       </c>
-      <c r="E86" t="s">
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D90" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D87" t="s">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="B91" t="s">
         <v>343</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C91" t="s">
         <v>344</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D91" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="E91" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D92" t="s">
         <v>346</v>
-      </c>
-      <c r="E88" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D89" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>137</v>
-      </c>
-      <c r="B90" t="s">
-        <v>348</v>
-      </c>
-      <c r="C90" t="s">
-        <v>349</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="E90" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D91" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>139</v>
-      </c>
-      <c r="B92" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B93" t="s">
-        <v>219</v>
+        <v>347</v>
       </c>
       <c r="C93" t="s">
-        <v>220</v>
+        <v>348</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>221</v>
+        <v>349</v>
       </c>
       <c r="E93" t="s">
-        <v>222</v>
+        <v>350</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D94" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>139</v>
+      </c>
+      <c r="B95" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>142</v>
+      </c>
+      <c r="B96" t="s">
+        <v>219</v>
+      </c>
+      <c r="C96" t="s">
+        <v>220</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E96" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C95" t="s">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C98" t="s">
+        <v>353</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="D95" s="4" t="s">
+      <c r="E98" t="s">
         <v>355</v>
       </c>
-      <c r="E95" t="s">
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D99" t="s">
         <v>356</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D96" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>146</v>
-      </c>
-      <c r="B97" t="s">
-        <v>358</v>
-      </c>
-      <c r="C97" t="s">
-        <v>359</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="E97" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D98" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C99" t="s">
-        <v>363</v>
-      </c>
-      <c r="D99" t="s">
-        <v>364</v>
-      </c>
-      <c r="E99" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>146</v>
+      </c>
+      <c r="B100" t="s">
+        <v>357</v>
+      </c>
+      <c r="C100" t="s">
+        <v>358</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="E100" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C102" t="s">
+        <v>362</v>
+      </c>
+      <c r="D102" t="s">
+        <v>363</v>
+      </c>
+      <c r="E102" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>151</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B103" t="s">
+        <v>365</v>
+      </c>
+      <c r="C103" t="s">
         <v>366</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D103" t="s">
         <v>367</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E103" t="s">
         <v>368</v>
       </c>
-      <c r="E100" t="s">
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="B104" t="s">
         <v>370</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C104" t="s">
         <v>371</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D104" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="D101" s="4" t="s">
+      <c r="E104" t="s">
         <v>373</v>
       </c>
-      <c r="E101" t="s">
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D105" t="s">
         <v>374</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D102" t="s">
-        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -3480,37 +3559,38 @@
     <hyperlink ref="D38" r:id="rId19" xr:uid="{FB0CEB0D-414A-4DDB-B16E-5D7FE525679D}"/>
     <hyperlink ref="D44" r:id="rId20" xr:uid="{66E8E2DE-DE2A-4BEE-A00B-FC70DA6E393B}"/>
     <hyperlink ref="D46" r:id="rId21" xr:uid="{00FE2312-A0AD-460C-8C88-BB78450EC048}"/>
-    <hyperlink ref="D48" r:id="rId22" xr:uid="{EE64A00F-896D-4A7E-B58D-6DADDC01E4EB}"/>
-    <hyperlink ref="D51" r:id="rId23" xr:uid="{B96EA048-73B5-4043-87FA-348516901FF7}"/>
-    <hyperlink ref="D52" r:id="rId24" xr:uid="{02F4630C-C267-4B48-B7EA-27E6788B9E77}"/>
-    <hyperlink ref="D101" r:id="rId25" xr:uid="{968BC9E8-238F-45ED-B3B6-9D3CB4D175EB}"/>
+    <hyperlink ref="D50" r:id="rId22" xr:uid="{EE64A00F-896D-4A7E-B58D-6DADDC01E4EB}"/>
+    <hyperlink ref="D54" r:id="rId23" xr:uid="{B96EA048-73B5-4043-87FA-348516901FF7}"/>
+    <hyperlink ref="D55" r:id="rId24" xr:uid="{02F4630C-C267-4B48-B7EA-27E6788B9E77}"/>
+    <hyperlink ref="D104" r:id="rId25" xr:uid="{968BC9E8-238F-45ED-B3B6-9D3CB4D175EB}"/>
     <hyperlink ref="D21" r:id="rId26" xr:uid="{0DBFFF51-A050-4AEF-BD67-2C3CB3782A78}"/>
     <hyperlink ref="D22" r:id="rId27" xr:uid="{EE8223A0-E92D-4A6C-8B78-75FC381E07CD}"/>
-    <hyperlink ref="D54" r:id="rId28" xr:uid="{7B455CBA-4520-4A7E-AB67-F75B720AF44C}"/>
-    <hyperlink ref="D55" r:id="rId29" xr:uid="{A083BFAA-62DD-422A-921A-A88401E2763B}"/>
-    <hyperlink ref="D56" r:id="rId30" xr:uid="{37F7100A-0AD9-4613-8F1B-A2292307919C}"/>
-    <hyperlink ref="D58" r:id="rId31" xr:uid="{9FC4A011-A3C7-4C98-BCE2-9F87A773F226}"/>
-    <hyperlink ref="D62" r:id="rId32" xr:uid="{4A37A47E-17B1-4DC8-879F-105DC38CA817}"/>
-    <hyperlink ref="D64" r:id="rId33" xr:uid="{14FC9A88-1D7E-4913-B4CB-69D4B6039B40}"/>
-    <hyperlink ref="D66" r:id="rId34" xr:uid="{94204ED1-5E6E-4F7C-BB6C-F07A5A7E912C}"/>
-    <hyperlink ref="D68" r:id="rId35" xr:uid="{DC6956D3-AE5F-4B8B-9308-37E343A1D251}"/>
-    <hyperlink ref="D70" r:id="rId36" xr:uid="{F3BC5CD7-304D-466C-8F3A-41A88A39A0F9}"/>
-    <hyperlink ref="D72" r:id="rId37" xr:uid="{FBE7E3B1-EBDD-4F3C-8586-C1F33B70D15C}"/>
-    <hyperlink ref="D74" r:id="rId38" xr:uid="{6B79EDD2-91AA-4DEE-B7EE-4ECF0C17832A}"/>
-    <hyperlink ref="D76" r:id="rId39" xr:uid="{DC821F99-AB92-4497-A547-E9F48D8345A1}"/>
-    <hyperlink ref="D79" r:id="rId40" xr:uid="{F2441D32-16E3-479E-9542-4267D844D72D}"/>
-    <hyperlink ref="D81" r:id="rId41" xr:uid="{E34CD9EC-8EBB-4336-B24D-EE724364893A}"/>
-    <hyperlink ref="D86" r:id="rId42" xr:uid="{A047E128-82EC-4C59-BAF2-FCD12D15CDF5}"/>
-    <hyperlink ref="D60" r:id="rId43" xr:uid="{86B7AF25-D7FF-4A64-A3BF-0FBE37A50540}"/>
-    <hyperlink ref="D90" r:id="rId44" xr:uid="{FBB3D187-828E-4EE5-9A3A-7DAB9E76A69F}"/>
-    <hyperlink ref="D93" r:id="rId45" xr:uid="{0A3F7BA5-315F-401E-80BC-F1538A6518D6}"/>
-    <hyperlink ref="D95" r:id="rId46" xr:uid="{F0711F6D-40BA-43B7-9ECF-B82978796DC2}"/>
-    <hyperlink ref="D97" r:id="rId47" xr:uid="{F7C374DA-140B-4F97-8D26-83DCC74C2C93}"/>
-    <hyperlink ref="D88" r:id="rId48" xr:uid="{3FCB7547-9F8C-4036-B219-7EB215FF8AA6}"/>
-    <hyperlink ref="D84" r:id="rId49" xr:uid="{575FB118-FAD6-4B64-8B08-A34ED533720A}"/>
+    <hyperlink ref="D57" r:id="rId28" xr:uid="{7B455CBA-4520-4A7E-AB67-F75B720AF44C}"/>
+    <hyperlink ref="D58" r:id="rId29" xr:uid="{A083BFAA-62DD-422A-921A-A88401E2763B}"/>
+    <hyperlink ref="D59" r:id="rId30" xr:uid="{37F7100A-0AD9-4613-8F1B-A2292307919C}"/>
+    <hyperlink ref="D61" r:id="rId31" xr:uid="{9FC4A011-A3C7-4C98-BCE2-9F87A773F226}"/>
+    <hyperlink ref="D65" r:id="rId32" xr:uid="{4A37A47E-17B1-4DC8-879F-105DC38CA817}"/>
+    <hyperlink ref="D67" r:id="rId33" xr:uid="{14FC9A88-1D7E-4913-B4CB-69D4B6039B40}"/>
+    <hyperlink ref="D69" r:id="rId34" xr:uid="{94204ED1-5E6E-4F7C-BB6C-F07A5A7E912C}"/>
+    <hyperlink ref="D71" r:id="rId35" xr:uid="{DC6956D3-AE5F-4B8B-9308-37E343A1D251}"/>
+    <hyperlink ref="D73" r:id="rId36" xr:uid="{F3BC5CD7-304D-466C-8F3A-41A88A39A0F9}"/>
+    <hyperlink ref="D75" r:id="rId37" xr:uid="{FBE7E3B1-EBDD-4F3C-8586-C1F33B70D15C}"/>
+    <hyperlink ref="D77" r:id="rId38" xr:uid="{6B79EDD2-91AA-4DEE-B7EE-4ECF0C17832A}"/>
+    <hyperlink ref="D79" r:id="rId39" xr:uid="{DC821F99-AB92-4497-A547-E9F48D8345A1}"/>
+    <hyperlink ref="D82" r:id="rId40" xr:uid="{F2441D32-16E3-479E-9542-4267D844D72D}"/>
+    <hyperlink ref="D84" r:id="rId41" xr:uid="{E34CD9EC-8EBB-4336-B24D-EE724364893A}"/>
+    <hyperlink ref="D89" r:id="rId42" xr:uid="{A047E128-82EC-4C59-BAF2-FCD12D15CDF5}"/>
+    <hyperlink ref="D63" r:id="rId43" xr:uid="{86B7AF25-D7FF-4A64-A3BF-0FBE37A50540}"/>
+    <hyperlink ref="D93" r:id="rId44" xr:uid="{FBB3D187-828E-4EE5-9A3A-7DAB9E76A69F}"/>
+    <hyperlink ref="D96" r:id="rId45" xr:uid="{0A3F7BA5-315F-401E-80BC-F1538A6518D6}"/>
+    <hyperlink ref="D98" r:id="rId46" xr:uid="{F0711F6D-40BA-43B7-9ECF-B82978796DC2}"/>
+    <hyperlink ref="D100" r:id="rId47" xr:uid="{F7C374DA-140B-4F97-8D26-83DCC74C2C93}"/>
+    <hyperlink ref="D91" r:id="rId48" xr:uid="{3FCB7547-9F8C-4036-B219-7EB215FF8AA6}"/>
+    <hyperlink ref="D87" r:id="rId49" xr:uid="{575FB118-FAD6-4B64-8B08-A34ED533720A}"/>
+    <hyperlink ref="D51" r:id="rId50" xr:uid="{08AE1140-BF34-42D5-A454-14277BADE0DC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId51"/>
 </worksheet>
 </file>
 
